--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,1227 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127743774</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>630589</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6964199</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127743775</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>630579</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6964196</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127743779</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79052</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>185</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>630484</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6964173</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127743768</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>630474</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6964289</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127743770</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>630512</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6964262</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127743773</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>630567</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6964209</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127743772</v>
+      </c>
+      <c r="B9" t="n">
+        <v>82861</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>630571</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6964222</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127743769</v>
+      </c>
+      <c r="B10" t="n">
+        <v>82861</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>630496</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6964277</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127743767</v>
+      </c>
+      <c r="B11" t="n">
+        <v>82861</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>630374</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6964238</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127743766</v>
+      </c>
+      <c r="B12" t="n">
+        <v>77998</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>630343</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6964256</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127743771</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91343</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gältjärn, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>630509</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6964256</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127743775</v>
+        <v>127743779</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630579</v>
+        <v>630484</v>
       </c>
       <c r="R4" t="n">
-        <v>6964196</v>
+        <v>6964173</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,22 +980,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127743779</v>
+        <v>127743775</v>
       </c>
       <c r="B5" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630484</v>
+        <v>630579</v>
       </c>
       <c r="R5" t="n">
-        <v>6964173</v>
+        <v>6964196</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1091,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127743770</v>
+        <v>127743773</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630512</v>
+        <v>630567</v>
       </c>
       <c r="R7" t="n">
-        <v>6964262</v>
+        <v>6964209</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743773</v>
+        <v>127743772</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>82861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630567</v>
+        <v>630571</v>
       </c>
       <c r="R8" t="n">
-        <v>6964209</v>
+        <v>6964222</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1466,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743772</v>
+        <v>127743770</v>
       </c>
       <c r="B9" t="n">
-        <v>82861</v>
+        <v>80083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630571</v>
+        <v>630512</v>
       </c>
       <c r="R9" t="n">
-        <v>6964222</v>
+        <v>6964262</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127743773</v>
+        <v>127743772</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>82861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630567</v>
+        <v>630571</v>
       </c>
       <c r="R7" t="n">
-        <v>6964209</v>
+        <v>6964222</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743772</v>
+        <v>127743773</v>
       </c>
       <c r="B8" t="n">
-        <v>82861</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630571</v>
+        <v>630567</v>
       </c>
       <c r="R8" t="n">
-        <v>6964222</v>
+        <v>6964209</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127743774</v>
       </c>
       <c r="B3" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>127743768</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127743772</v>
+        <v>127743773</v>
       </c>
       <c r="B7" t="n">
-        <v>82861</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630571</v>
+        <v>630567</v>
       </c>
       <c r="R7" t="n">
-        <v>6964222</v>
+        <v>6964209</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,32 +1355,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743773</v>
+        <v>127743770</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>80083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630567</v>
+        <v>630512</v>
       </c>
       <c r="R8" t="n">
-        <v>6964209</v>
+        <v>6964262</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1466,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743770</v>
+        <v>127743772</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>82861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630512</v>
+        <v>630571</v>
       </c>
       <c r="R9" t="n">
-        <v>6964262</v>
+        <v>6964222</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1913,7 +1913,7 @@
         <v>127743771</v>
       </c>
       <c r="B13" t="n">
-        <v>91343</v>
+        <v>91349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127743774</v>
       </c>
       <c r="B3" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127743779</v>
+        <v>127743775</v>
       </c>
       <c r="B4" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630484</v>
+        <v>630579</v>
       </c>
       <c r="R4" t="n">
-        <v>6964173</v>
+        <v>6964196</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,22 +980,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127743775</v>
+        <v>127743779</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630579</v>
+        <v>630484</v>
       </c>
       <c r="R5" t="n">
-        <v>6964196</v>
+        <v>6964173</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1091,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
         <v>127743768</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127743773</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>127743770</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>127743772</v>
       </c>
       <c r="B9" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>127743769</v>
       </c>
       <c r="B10" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>127743767</v>
       </c>
       <c r="B11" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127743766</v>
       </c>
       <c r="B12" t="n">
-        <v>77998</v>
+        <v>78001</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>127743771</v>
       </c>
       <c r="B13" t="n">
-        <v>91349</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127743774</v>
       </c>
       <c r="B3" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127743775</v>
+        <v>127743779</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630579</v>
+        <v>630484</v>
       </c>
       <c r="R4" t="n">
-        <v>6964196</v>
+        <v>6964173</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,22 +980,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127743779</v>
+        <v>127743775</v>
       </c>
       <c r="B5" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630484</v>
+        <v>630579</v>
       </c>
       <c r="R5" t="n">
-        <v>6964173</v>
+        <v>6964196</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1091,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
         <v>127743768</v>
       </c>
       <c r="B6" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127743773</v>
+        <v>127743770</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>80092</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630567</v>
+        <v>630512</v>
       </c>
       <c r="R7" t="n">
-        <v>6964209</v>
+        <v>6964262</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,32 +1355,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743770</v>
+        <v>127743772</v>
       </c>
       <c r="B8" t="n">
-        <v>80086</v>
+        <v>82870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630512</v>
+        <v>630571</v>
       </c>
       <c r="R8" t="n">
-        <v>6964262</v>
+        <v>6964222</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743772</v>
+        <v>127743773</v>
       </c>
       <c r="B9" t="n">
-        <v>82864</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630571</v>
+        <v>630567</v>
       </c>
       <c r="R9" t="n">
-        <v>6964222</v>
+        <v>6964209</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,7 +1580,7 @@
         <v>127743769</v>
       </c>
       <c r="B10" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>127743767</v>
       </c>
       <c r="B11" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127743766</v>
       </c>
       <c r="B12" t="n">
-        <v>78001</v>
+        <v>78007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>127743771</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127743774</v>
       </c>
       <c r="B3" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>127743768</v>
       </c>
       <c r="B6" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127743770</v>
+        <v>127743772</v>
       </c>
       <c r="B7" t="n">
-        <v>80092</v>
+        <v>82870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630512</v>
+        <v>630571</v>
       </c>
       <c r="R7" t="n">
-        <v>6964262</v>
+        <v>6964222</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743772</v>
+        <v>127743773</v>
       </c>
       <c r="B8" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630571</v>
+        <v>630567</v>
       </c>
       <c r="R8" t="n">
-        <v>6964222</v>
+        <v>6964209</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1466,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743773</v>
+        <v>127743770</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>80092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630567</v>
+        <v>630512</v>
       </c>
       <c r="R9" t="n">
-        <v>6964209</v>
+        <v>6964262</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127743767</v>
+        <v>127743766</v>
       </c>
       <c r="B11" t="n">
-        <v>82870</v>
+        <v>78007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630374</v>
+        <v>630343</v>
       </c>
       <c r="R11" t="n">
-        <v>6964238</v>
+        <v>6964256</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127743766</v>
+        <v>127743767</v>
       </c>
       <c r="B12" t="n">
-        <v>78007</v>
+        <v>82870</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630343</v>
+        <v>630374</v>
       </c>
       <c r="R12" t="n">
-        <v>6964256</v>
+        <v>6964238</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,7 +1913,7 @@
         <v>127743771</v>
       </c>
       <c r="B13" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -1355,32 +1355,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743773</v>
+        <v>127743770</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>80092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630567</v>
+        <v>630512</v>
       </c>
       <c r="R8" t="n">
-        <v>6964209</v>
+        <v>6964262</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1466,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743770</v>
+        <v>127743773</v>
       </c>
       <c r="B9" t="n">
-        <v>80092</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630512</v>
+        <v>630567</v>
       </c>
       <c r="R9" t="n">
-        <v>6964262</v>
+        <v>6964209</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127743766</v>
+        <v>127743767</v>
       </c>
       <c r="B11" t="n">
-        <v>78007</v>
+        <v>82870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630343</v>
+        <v>630374</v>
       </c>
       <c r="R11" t="n">
-        <v>6964256</v>
+        <v>6964238</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127743767</v>
+        <v>127743766</v>
       </c>
       <c r="B12" t="n">
-        <v>82870</v>
+        <v>78007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630374</v>
+        <v>630343</v>
       </c>
       <c r="R12" t="n">
-        <v>6964238</v>
+        <v>6964256</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127743774</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>127743768</v>
       </c>
       <c r="B6" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743770</v>
+        <v>127743773</v>
       </c>
       <c r="B8" t="n">
-        <v>80092</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630512</v>
+        <v>630567</v>
       </c>
       <c r="R8" t="n">
-        <v>6964262</v>
+        <v>6964209</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1466,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743773</v>
+        <v>127743770</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>80092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630567</v>
+        <v>630512</v>
       </c>
       <c r="R9" t="n">
-        <v>6964209</v>
+        <v>6964262</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1913,7 +1913,7 @@
         <v>127743771</v>
       </c>
       <c r="B13" t="n">
-        <v>91361</v>
+        <v>91362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127743774</v>
       </c>
       <c r="B3" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>127743768</v>
       </c>
       <c r="B6" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1355,32 +1355,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743773</v>
+        <v>127743770</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>80092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630567</v>
+        <v>630512</v>
       </c>
       <c r="R8" t="n">
-        <v>6964209</v>
+        <v>6964262</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1466,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743770</v>
+        <v>127743773</v>
       </c>
       <c r="B9" t="n">
-        <v>80092</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630512</v>
+        <v>630567</v>
       </c>
       <c r="R9" t="n">
-        <v>6964262</v>
+        <v>6964209</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1913,7 +1913,7 @@
         <v>127743771</v>
       </c>
       <c r="B13" t="n">
-        <v>91362</v>
+        <v>91363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -1355,32 +1355,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743770</v>
+        <v>127743773</v>
       </c>
       <c r="B8" t="n">
-        <v>80092</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630512</v>
+        <v>630567</v>
       </c>
       <c r="R8" t="n">
-        <v>6964262</v>
+        <v>6964209</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1466,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743773</v>
+        <v>127743770</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>80092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630567</v>
+        <v>630512</v>
       </c>
       <c r="R9" t="n">
-        <v>6964209</v>
+        <v>6964262</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127743767</v>
+        <v>127743766</v>
       </c>
       <c r="B11" t="n">
-        <v>82870</v>
+        <v>78007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630374</v>
+        <v>630343</v>
       </c>
       <c r="R11" t="n">
-        <v>6964238</v>
+        <v>6964256</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127743766</v>
+        <v>127743767</v>
       </c>
       <c r="B12" t="n">
-        <v>78007</v>
+        <v>82870</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630343</v>
+        <v>630374</v>
       </c>
       <c r="R12" t="n">
-        <v>6964256</v>
+        <v>6964238</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127743766</v>
+        <v>127743767</v>
       </c>
       <c r="B11" t="n">
-        <v>78007</v>
+        <v>82870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630343</v>
+        <v>630374</v>
       </c>
       <c r="R11" t="n">
-        <v>6964256</v>
+        <v>6964238</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127743767</v>
+        <v>127743766</v>
       </c>
       <c r="B12" t="n">
-        <v>82870</v>
+        <v>78007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630374</v>
+        <v>630343</v>
       </c>
       <c r="R12" t="n">
-        <v>6964238</v>
+        <v>6964256</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127743772</v>
+        <v>127743770</v>
       </c>
       <c r="B7" t="n">
-        <v>82870</v>
+        <v>80092</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630571</v>
+        <v>630512</v>
       </c>
       <c r="R7" t="n">
-        <v>6964222</v>
+        <v>6964262</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743773</v>
+        <v>127743772</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630567</v>
+        <v>630571</v>
       </c>
       <c r="R8" t="n">
-        <v>6964209</v>
+        <v>6964222</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1466,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743770</v>
+        <v>127743773</v>
       </c>
       <c r="B9" t="n">
-        <v>80092</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630512</v>
+        <v>630567</v>
       </c>
       <c r="R9" t="n">
-        <v>6964262</v>
+        <v>6964209</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127743767</v>
+        <v>127743766</v>
       </c>
       <c r="B11" t="n">
-        <v>82870</v>
+        <v>78007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630374</v>
+        <v>630343</v>
       </c>
       <c r="R11" t="n">
-        <v>6964238</v>
+        <v>6964256</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127743766</v>
+        <v>127743767</v>
       </c>
       <c r="B12" t="n">
-        <v>78007</v>
+        <v>82870</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630343</v>
+        <v>630374</v>
       </c>
       <c r="R12" t="n">
-        <v>6964256</v>
+        <v>6964238</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127743774</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>127743779</v>
       </c>
       <c r="B4" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>127743775</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>127743768</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>127743770</v>
       </c>
       <c r="B7" t="n">
-        <v>80092</v>
+        <v>80095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743772</v>
+        <v>127743773</v>
       </c>
       <c r="B8" t="n">
-        <v>82870</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630571</v>
+        <v>630567</v>
       </c>
       <c r="R8" t="n">
-        <v>6964222</v>
+        <v>6964209</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743773</v>
+        <v>127743772</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>82873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630567</v>
+        <v>630571</v>
       </c>
       <c r="R9" t="n">
-        <v>6964209</v>
+        <v>6964222</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,7 +1580,7 @@
         <v>127743769</v>
       </c>
       <c r="B10" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>127743767</v>
       </c>
       <c r="B11" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127743766</v>
       </c>
       <c r="B12" t="n">
-        <v>78007</v>
+        <v>78010</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>127743771</v>
       </c>
       <c r="B13" t="n">
-        <v>91363</v>
+        <v>91371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127743770</v>
+        <v>127743773</v>
       </c>
       <c r="B7" t="n">
-        <v>80095</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630512</v>
+        <v>630567</v>
       </c>
       <c r="R7" t="n">
-        <v>6964262</v>
+        <v>6964209</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743773</v>
+        <v>127743772</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>82873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630567</v>
+        <v>630571</v>
       </c>
       <c r="R8" t="n">
-        <v>6964209</v>
+        <v>6964222</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,32 +1466,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127743772</v>
+        <v>127743770</v>
       </c>
       <c r="B9" t="n">
-        <v>82873</v>
+        <v>80095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630571</v>
+        <v>630512</v>
       </c>
       <c r="R9" t="n">
-        <v>6964222</v>
+        <v>6964262</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>127743774</v>
       </c>
       <c r="B3" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>127743779</v>
       </c>
       <c r="B4" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>127743775</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>127743768</v>
       </c>
       <c r="B6" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127743773</v>
+        <v>127743772</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>82942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630567</v>
+        <v>630571</v>
       </c>
       <c r="R7" t="n">
-        <v>6964209</v>
+        <v>6964222</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127743772</v>
+        <v>127743773</v>
       </c>
       <c r="B8" t="n">
-        <v>82873</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630571</v>
+        <v>630567</v>
       </c>
       <c r="R8" t="n">
-        <v>6964222</v>
+        <v>6964209</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1469,7 @@
         <v>127743770</v>
       </c>
       <c r="B9" t="n">
-        <v>80095</v>
+        <v>80148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>127743769</v>
       </c>
       <c r="B10" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>127743767</v>
       </c>
       <c r="B11" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127743766</v>
       </c>
       <c r="B12" t="n">
-        <v>78010</v>
+        <v>78055</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>127743771</v>
       </c>
       <c r="B13" t="n">
-        <v>91371</v>
+        <v>91463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2019,6 +2019,2220 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129460944</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>630453</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6964277</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129459491</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>630580</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6964199</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129459847</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80184</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>630543</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6964253</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129460199</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80177</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>630512</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6964259</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129461963</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>630385</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6964224</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129461993</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>630386</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6964210</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129460507</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>630460</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6964259</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129461775</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>630308</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6964263</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129461528</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>630357</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6964257</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129460582</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80183</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>630474</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6964266</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129462120</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>630429</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6964216</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129462386</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>630500</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6964206</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129460877</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95936</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>630473</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6964282</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129461176</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>630429</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6964260</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129459217</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>630633</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6964165</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129462689</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57568</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>630526</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6964178</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129460244</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80108</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>630499</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6964259</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129462293</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>630480</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6964205</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129460703</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97581</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>630473</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6964282</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129461655</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>630325</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6964260</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129459722</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>630537</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6964211</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129460267</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>630499</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6964259</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>129459847</v>
       </c>
       <c r="B16" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,45 +2312,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129460199</v>
+        <v>129461963</v>
       </c>
       <c r="B17" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630512</v>
+        <v>630385</v>
       </c>
       <c r="R17" t="n">
-        <v>6964259</v>
+        <v>6964224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2383,6 +2388,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,50 +2419,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129461963</v>
+        <v>129460199</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630385</v>
+        <v>630512</v>
       </c>
       <c r="R18" t="n">
-        <v>6964224</v>
+        <v>6964259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B23" t="n">
-        <v>80183</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R23" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>80184</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R24" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,45 +3235,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B26" t="n">
-        <v>95936</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R26" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,6 +3311,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3332,50 +3342,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>95938</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R27" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,11 +3413,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,7 +3646,7 @@
         <v>129460244</v>
       </c>
       <c r="B30" t="n">
-        <v>80108</v>
+        <v>80109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>129462293</v>
       </c>
       <c r="B31" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>129460703</v>
       </c>
       <c r="B32" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>129460267</v>
       </c>
       <c r="B35" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,6 +4232,103 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129462589</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91769</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Torpkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>630503</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6964171</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stigsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3235,50 +3235,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>95942</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R26" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,11 +3306,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,45 +3332,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B27" t="n">
-        <v>95938</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R27" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,6 +3408,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129460244</v>
+        <v>129462293</v>
       </c>
       <c r="B30" t="n">
-        <v>80109</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630499</v>
+        <v>630480</v>
       </c>
       <c r="R30" t="n">
-        <v>6964259</v>
+        <v>6964205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,32 +3740,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129462293</v>
+        <v>129460244</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630480</v>
+        <v>630499</v>
       </c>
       <c r="R31" t="n">
-        <v>6964205</v>
+        <v>6964259</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,45 +3837,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129460703</v>
+        <v>129461655</v>
       </c>
       <c r="B32" t="n">
-        <v>97583</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630473</v>
+        <v>630325</v>
       </c>
       <c r="R32" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,6 +3913,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3934,50 +3944,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129461655</v>
+        <v>129460703</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>97587</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630325</v>
+        <v>630473</v>
       </c>
       <c r="R33" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4010,11 +4015,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129462589</v>
       </c>
       <c r="B36" t="n">
-        <v>91769</v>
+        <v>91773</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R23" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B24" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R24" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,7 +3238,7 @@
         <v>129460877</v>
       </c>
       <c r="B26" t="n">
-        <v>95942</v>
+        <v>95950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3837,50 +3837,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129461655</v>
+        <v>129460703</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>97595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630325</v>
+        <v>630473</v>
       </c>
       <c r="R32" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3913,11 +3908,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3944,45 +3934,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129460703</v>
+        <v>129461655</v>
       </c>
       <c r="B33" t="n">
-        <v>97587</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630473</v>
+        <v>630325</v>
       </c>
       <c r="R33" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4015,6 +4010,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129462589</v>
       </c>
       <c r="B36" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R19" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,11 +2592,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,16 +2629,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2654,7 +2649,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2663,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R20" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,6 +2694,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B23" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R23" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R24" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129462293</v>
+        <v>129460244</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630480</v>
+        <v>630499</v>
       </c>
       <c r="R30" t="n">
-        <v>6964205</v>
+        <v>6964259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,32 +3740,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129460244</v>
+        <v>129462293</v>
       </c>
       <c r="B31" t="n">
-        <v>80109</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630499</v>
+        <v>630480</v>
       </c>
       <c r="R31" t="n">
-        <v>6964259</v>
+        <v>6964205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,45 +3837,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129460703</v>
+        <v>129461655</v>
       </c>
       <c r="B32" t="n">
-        <v>97595</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630473</v>
+        <v>630325</v>
       </c>
       <c r="R32" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,6 +3913,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3934,50 +3944,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129461655</v>
+        <v>129460703</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>97595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630325</v>
+        <v>630473</v>
       </c>
       <c r="R33" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4010,11 +4015,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -3837,50 +3837,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129461655</v>
+        <v>129460703</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>97595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630325</v>
+        <v>630473</v>
       </c>
       <c r="R32" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3913,11 +3908,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3944,45 +3934,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129460703</v>
+        <v>129461655</v>
       </c>
       <c r="B33" t="n">
-        <v>97595</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630473</v>
+        <v>630325</v>
       </c>
       <c r="R33" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4015,6 +4010,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,50 +2312,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129461963</v>
+        <v>129460199</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630385</v>
+        <v>630512</v>
       </c>
       <c r="R17" t="n">
-        <v>6964224</v>
+        <v>6964259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,11 +2383,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,45 +2409,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129460199</v>
+        <v>129461963</v>
       </c>
       <c r="B18" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630512</v>
+        <v>630385</v>
       </c>
       <c r="R18" t="n">
-        <v>6964259</v>
+        <v>6964224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,6 +2485,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R19" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,6 +2592,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,16 +2634,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2649,7 +2654,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2658,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R20" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,11 +2699,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3238,7 +3238,7 @@
         <v>129460877</v>
       </c>
       <c r="B26" t="n">
-        <v>95950</v>
+        <v>95953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129460244</v>
+        <v>129462293</v>
       </c>
       <c r="B30" t="n">
-        <v>80109</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630499</v>
+        <v>630480</v>
       </c>
       <c r="R30" t="n">
-        <v>6964259</v>
+        <v>6964205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,32 +3740,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129462293</v>
+        <v>129460244</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630480</v>
+        <v>630499</v>
       </c>
       <c r="R31" t="n">
-        <v>6964205</v>
+        <v>6964259</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,45 +3837,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129460703</v>
+        <v>129461655</v>
       </c>
       <c r="B32" t="n">
-        <v>97595</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630473</v>
+        <v>630325</v>
       </c>
       <c r="R32" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,6 +3913,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3934,50 +3944,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129461655</v>
+        <v>129460703</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>97598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630325</v>
+        <v>630473</v>
       </c>
       <c r="R33" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4010,11 +4015,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129462589</v>
       </c>
       <c r="B36" t="n">
-        <v>91774</v>
+        <v>91777</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R19" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,11 +2592,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,16 +2629,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2654,7 +2649,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2663,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R20" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,6 +2694,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3837,50 +3837,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129461655</v>
+        <v>129460703</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>97598</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630325</v>
+        <v>630473</v>
       </c>
       <c r="R32" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3913,11 +3908,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3944,45 +3934,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129460703</v>
+        <v>129461655</v>
       </c>
       <c r="B33" t="n">
-        <v>97598</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630473</v>
+        <v>630325</v>
       </c>
       <c r="R33" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4015,6 +4010,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R23" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B24" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R24" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129462293</v>
+        <v>129460244</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630480</v>
+        <v>630499</v>
       </c>
       <c r="R30" t="n">
-        <v>6964205</v>
+        <v>6964259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,32 +3740,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129460244</v>
+        <v>129462293</v>
       </c>
       <c r="B31" t="n">
-        <v>80109</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630499</v>
+        <v>630480</v>
       </c>
       <c r="R31" t="n">
-        <v>6964259</v>
+        <v>6964205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,45 +3837,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129460703</v>
+        <v>129461655</v>
       </c>
       <c r="B32" t="n">
-        <v>97598</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630473</v>
+        <v>630325</v>
       </c>
       <c r="R32" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,6 +3913,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3934,50 +3944,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129461655</v>
+        <v>129460703</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>97598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630325</v>
+        <v>630473</v>
       </c>
       <c r="R33" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4010,11 +4015,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B23" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R23" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R24" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,45 +3235,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B26" t="n">
-        <v>95953</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R26" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,6 +3311,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3332,50 +3342,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>95953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R27" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,11 +3413,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129460244</v>
+        <v>129462293</v>
       </c>
       <c r="B30" t="n">
-        <v>80109</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630499</v>
+        <v>630480</v>
       </c>
       <c r="R30" t="n">
-        <v>6964259</v>
+        <v>6964205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,32 +3740,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129462293</v>
+        <v>129460244</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630480</v>
+        <v>630499</v>
       </c>
       <c r="R31" t="n">
-        <v>6964205</v>
+        <v>6964259</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -3235,50 +3235,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>95953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R26" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,11 +3306,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,45 +3332,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B27" t="n">
-        <v>95953</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R27" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,6 +3408,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129462293</v>
+        <v>129460244</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630480</v>
+        <v>630499</v>
       </c>
       <c r="R30" t="n">
-        <v>6964205</v>
+        <v>6964259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,32 +3740,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129460244</v>
+        <v>129462293</v>
       </c>
       <c r="B31" t="n">
-        <v>80109</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630499</v>
+        <v>630480</v>
       </c>
       <c r="R31" t="n">
-        <v>6964259</v>
+        <v>6964205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2312,45 +2312,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129460199</v>
+        <v>129461963</v>
       </c>
       <c r="B17" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630512</v>
+        <v>630385</v>
       </c>
       <c r="R17" t="n">
-        <v>6964259</v>
+        <v>6964224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2383,6 +2388,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,50 +2419,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129461963</v>
+        <v>129460199</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630385</v>
+        <v>630512</v>
       </c>
       <c r="R18" t="n">
-        <v>6964224</v>
+        <v>6964259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>129459847</v>
       </c>
       <c r="B16" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>129461963</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>129460199</v>
       </c>
       <c r="B18" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R19" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,6 +2592,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,7 +2623,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2629,16 +2634,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2649,7 +2654,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2658,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R20" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,11 +2699,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,7 +2728,7 @@
         <v>129461775</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>129461528</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>129462120</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>129460582</v>
       </c>
       <c r="B24" t="n">
-        <v>80184</v>
+        <v>80210</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129462386</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,45 +3235,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B26" t="n">
-        <v>95953</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R26" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,6 +3311,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3332,50 +3342,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>95982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R27" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,11 +3413,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,7 +3442,7 @@
         <v>129459217</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>129462689</v>
       </c>
       <c r="B29" t="n">
-        <v>57568</v>
+        <v>57571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>129460244</v>
       </c>
       <c r="B30" t="n">
-        <v>80109</v>
+        <v>80135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>129462293</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>129461655</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>129460703</v>
       </c>
       <c r="B33" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>129460267</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129462589</v>
       </c>
       <c r="B36" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2312,50 +2312,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129461963</v>
+        <v>129460199</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>80204</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630385</v>
+        <v>630512</v>
       </c>
       <c r="R17" t="n">
-        <v>6964224</v>
+        <v>6964259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,11 +2383,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,45 +2409,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129460199</v>
+        <v>129461963</v>
       </c>
       <c r="B18" t="n">
-        <v>80204</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630512</v>
+        <v>630385</v>
       </c>
       <c r="R18" t="n">
-        <v>6964259</v>
+        <v>6964224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,6 +2485,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3235,50 +3235,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>95982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R26" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,11 +3306,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,45 +3332,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B27" t="n">
-        <v>95982</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R27" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,6 +3408,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>129459847</v>
       </c>
       <c r="B16" t="n">
-        <v>80211</v>
+        <v>80216</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>129460199</v>
       </c>
       <c r="B17" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>129461963</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>57732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R19" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,11 +2592,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,16 +2629,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2654,7 +2649,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2663,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R20" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,6 +2694,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,7 +2728,7 @@
         <v>129461775</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>129461528</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>129462120</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>129460582</v>
       </c>
       <c r="B24" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129462386</v>
       </c>
       <c r="B25" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,45 +3235,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B26" t="n">
-        <v>95982</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R26" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,6 +3311,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3332,50 +3342,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>95994</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R27" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,11 +3413,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,7 +3442,7 @@
         <v>129459217</v>
       </c>
       <c r="B28" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>129462689</v>
       </c>
       <c r="B29" t="n">
-        <v>57571</v>
+        <v>57576</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129460244</v>
+        <v>129462293</v>
       </c>
       <c r="B30" t="n">
-        <v>80135</v>
+        <v>80180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630499</v>
+        <v>630480</v>
       </c>
       <c r="R30" t="n">
-        <v>6964259</v>
+        <v>6964205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,32 +3740,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129462293</v>
+        <v>129460244</v>
       </c>
       <c r="B31" t="n">
-        <v>80175</v>
+        <v>80140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630480</v>
+        <v>630499</v>
       </c>
       <c r="R31" t="n">
-        <v>6964205</v>
+        <v>6964259</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
         <v>129461655</v>
       </c>
       <c r="B32" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>129460703</v>
       </c>
       <c r="B33" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>129460267</v>
       </c>
       <c r="B35" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129462589</v>
       </c>
       <c r="B36" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>129459847</v>
       </c>
       <c r="B16" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>129460199</v>
       </c>
       <c r="B17" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>129461963</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B19" t="n">
-        <v>57732</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R19" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,6 +2592,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,16 +2634,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2649,7 +2654,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2658,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R20" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,11 +2699,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,7 +2728,7 @@
         <v>129461775</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>129461528</v>
       </c>
       <c r="B22" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B23" t="n">
-        <v>80180</v>
+        <v>80216</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R23" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B24" t="n">
-        <v>80215</v>
+        <v>80181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R24" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,7 +3136,7 @@
         <v>129462386</v>
       </c>
       <c r="B25" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>129461176</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>129460877</v>
       </c>
       <c r="B27" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>129459217</v>
       </c>
       <c r="B28" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>129462689</v>
       </c>
       <c r="B29" t="n">
-        <v>57576</v>
+        <v>57577</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>129462293</v>
       </c>
       <c r="B30" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>129460244</v>
       </c>
       <c r="B31" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>129461655</v>
       </c>
       <c r="B32" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>129460703</v>
       </c>
       <c r="B33" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>129460267</v>
       </c>
       <c r="B35" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129462589</v>
       </c>
       <c r="B36" t="n">
-        <v>91811</v>
+        <v>91812</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2312,45 +2312,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129460199</v>
+        <v>129461963</v>
       </c>
       <c r="B17" t="n">
-        <v>80210</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630512</v>
+        <v>630385</v>
       </c>
       <c r="R17" t="n">
-        <v>6964259</v>
+        <v>6964224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2383,6 +2388,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,50 +2419,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129461963</v>
+        <v>129460199</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>80210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630385</v>
+        <v>630512</v>
       </c>
       <c r="R18" t="n">
-        <v>6964224</v>
+        <v>6964259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B23" t="n">
-        <v>80216</v>
+        <v>80181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R23" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B24" t="n">
-        <v>80181</v>
+        <v>80216</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R24" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>129459847</v>
       </c>
       <c r="B16" t="n">
-        <v>80217</v>
+        <v>80222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>129460199</v>
       </c>
       <c r="B18" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R19" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,11 +2592,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,16 +2629,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2654,7 +2649,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2663,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R20" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,6 +2694,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2942,7 +2942,7 @@
         <v>129462120</v>
       </c>
       <c r="B23" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>129460582</v>
       </c>
       <c r="B24" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>129460877</v>
       </c>
       <c r="B27" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>129462293</v>
       </c>
       <c r="B30" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>129460244</v>
       </c>
       <c r="B31" t="n">
-        <v>80141</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>129460703</v>
       </c>
       <c r="B33" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>129460267</v>
       </c>
       <c r="B35" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129462589</v>
       </c>
       <c r="B36" t="n">
-        <v>91812</v>
+        <v>91817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2312,50 +2312,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129461963</v>
+        <v>129460199</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630385</v>
+        <v>630512</v>
       </c>
       <c r="R17" t="n">
-        <v>6964224</v>
+        <v>6964259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,11 +2383,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,45 +2409,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129460199</v>
+        <v>129461963</v>
       </c>
       <c r="B18" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630512</v>
+        <v>630385</v>
       </c>
       <c r="R18" t="n">
-        <v>6964259</v>
+        <v>6964224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,6 +2485,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B23" t="n">
-        <v>80186</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R23" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B24" t="n">
-        <v>80221</v>
+        <v>80186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R24" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,50 +3235,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>96000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R26" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,11 +3306,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,45 +3332,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B27" t="n">
-        <v>96000</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R27" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,6 +3408,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129462293</v>
+        <v>129460244</v>
       </c>
       <c r="B30" t="n">
-        <v>80186</v>
+        <v>80146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630480</v>
+        <v>630499</v>
       </c>
       <c r="R30" t="n">
-        <v>6964205</v>
+        <v>6964259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,32 +3740,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129460244</v>
+        <v>129462293</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630499</v>
+        <v>630480</v>
       </c>
       <c r="R31" t="n">
-        <v>6964259</v>
+        <v>6964205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2312,45 +2312,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129460199</v>
+        <v>129461963</v>
       </c>
       <c r="B17" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630512</v>
+        <v>630385</v>
       </c>
       <c r="R17" t="n">
-        <v>6964259</v>
+        <v>6964224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2383,6 +2388,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,50 +2419,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129461963</v>
+        <v>129460199</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630385</v>
+        <v>630512</v>
       </c>
       <c r="R18" t="n">
-        <v>6964224</v>
+        <v>6964259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R19" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,6 +2592,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,16 +2634,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2649,7 +2654,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2658,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R20" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,11 +2699,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2312,50 +2312,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129461963</v>
+        <v>129460199</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630385</v>
+        <v>630512</v>
       </c>
       <c r="R17" t="n">
-        <v>6964224</v>
+        <v>6964259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,11 +2383,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,45 +2409,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129460199</v>
+        <v>129461963</v>
       </c>
       <c r="B18" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630512</v>
+        <v>630385</v>
       </c>
       <c r="R18" t="n">
-        <v>6964259</v>
+        <v>6964224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,6 +2485,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>80186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R23" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B24" t="n">
-        <v>80186</v>
+        <v>80221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R24" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,45 +3235,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B26" t="n">
-        <v>96000</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R26" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,6 +3311,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3332,50 +3342,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>96000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R27" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,11 +3413,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129460244</v>
+        <v>129462293</v>
       </c>
       <c r="B30" t="n">
-        <v>80146</v>
+        <v>80186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630499</v>
+        <v>630480</v>
       </c>
       <c r="R30" t="n">
-        <v>6964259</v>
+        <v>6964205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,32 +3740,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129462293</v>
+        <v>129460244</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630480</v>
+        <v>630499</v>
       </c>
       <c r="R31" t="n">
-        <v>6964205</v>
+        <v>6964259</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R19" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,11 +2592,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,16 +2629,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2654,7 +2649,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2663,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R20" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,6 +2694,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3345,7 +3345,7 @@
         <v>129460877</v>
       </c>
       <c r="B27" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3837,50 +3837,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129461655</v>
+        <v>129460703</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>97649</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630325</v>
+        <v>630473</v>
       </c>
       <c r="R32" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3913,11 +3908,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3944,45 +3934,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129460703</v>
+        <v>129461655</v>
       </c>
       <c r="B33" t="n">
-        <v>97645</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630473</v>
+        <v>630325</v>
       </c>
       <c r="R33" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4015,6 +4010,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129462589</v>
       </c>
       <c r="B36" t="n">
-        <v>91817</v>
+        <v>91821</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>129460944</v>
       </c>
       <c r="B14" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>129459491</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,45 +2312,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129460199</v>
+        <v>129461963</v>
       </c>
       <c r="B17" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630512</v>
+        <v>630385</v>
       </c>
       <c r="R17" t="n">
-        <v>6964259</v>
+        <v>6964224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2383,6 +2388,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,50 +2419,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129461963</v>
+        <v>129460199</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630385</v>
+        <v>630512</v>
       </c>
       <c r="R18" t="n">
-        <v>6964224</v>
+        <v>6964259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,11 +2490,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129460507</v>
+        <v>129461993</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630460</v>
+        <v>630386</v>
       </c>
       <c r="R19" t="n">
-        <v>6964259</v>
+        <v>6964210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,6 +2592,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129461993</v>
+        <v>129460507</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,16 +2634,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2649,7 +2654,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2658,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630386</v>
+        <v>630460</v>
       </c>
       <c r="R20" t="n">
-        <v>6964210</v>
+        <v>6964259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,11 +2699,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B23" t="n">
-        <v>80186</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R23" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B24" t="n">
-        <v>80221</v>
+        <v>80186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R24" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3235,50 +3235,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129461176</v>
+        <v>129460877</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>96006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630429</v>
+        <v>630473</v>
       </c>
       <c r="R26" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,11 +3306,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,45 +3332,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129460877</v>
+        <v>129461176</v>
       </c>
       <c r="B27" t="n">
-        <v>96004</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630473</v>
+        <v>630429</v>
       </c>
       <c r="R27" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,6 +3408,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3837,45 +3837,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129460703</v>
+        <v>129461655</v>
       </c>
       <c r="B32" t="n">
-        <v>97649</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630473</v>
+        <v>630325</v>
       </c>
       <c r="R32" t="n">
-        <v>6964282</v>
+        <v>6964260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,6 +3913,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3934,50 +3944,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129461655</v>
+        <v>129460703</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>97651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Torpkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630325</v>
+        <v>630473</v>
       </c>
       <c r="R33" t="n">
-        <v>6964260</v>
+        <v>6964282</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4010,11 +4015,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4044,7 +4044,7 @@
         <v>129459722</v>
       </c>
       <c r="B34" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>129462589</v>
       </c>
       <c r="B36" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 34141-2025 artfynd.xlsx
+++ b/artfynd/A 34141-2025 artfynd.xlsx
@@ -2939,32 +2939,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129460582</v>
+        <v>129462120</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>80186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630474</v>
+        <v>630429</v>
       </c>
       <c r="R23" t="n">
-        <v>6964266</v>
+        <v>6964216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,32 +3036,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129462120</v>
+        <v>129460582</v>
       </c>
       <c r="B24" t="n">
-        <v>80186</v>
+        <v>80221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630429</v>
+        <v>630474</v>
       </c>
       <c r="R24" t="n">
-        <v>6964216</v>
+        <v>6964266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
